--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484222_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484222_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9305</v>
+        <v>3.0805</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6067</v>
+        <v>1.5661</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3237</v>
+        <v>1.5144</v>
       </c>
       <c r="G2" t="n">
         <v>2.1177</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.082</v>
+        <v>0.068</v>
       </c>
       <c r="T2" t="n">
-        <v>0.278</v>
+        <v>0.2374</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.36</v>
+        <v>-0.1694</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2772</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8099</v>
+        <v>1.5285</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5022</v>
+        <v>-0.1691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3078</v>
+        <v>1.6977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1715</v>
+        <v>2.2441</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.593</v>
+        <v>-2.5314</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7645</v>
+        <v>4.7755</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6105</v>
+        <v>2.1392</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3457</v>
+        <v>-1.4237</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9562</v>
+        <v>3.563</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.439</v>
+        <v>0.1049</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2474</v>
+        <v>-1.1077</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8083</v>
+        <v>1.2126</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R3" t="n">
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5836</v>
+        <v>-0.1761</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0953</v>
+        <v>-0.4015</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4884</v>
+        <v>0.2254</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7731</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>M. KIRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0999</v>
+        <v>1.4883</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8157</v>
+        <v>1.8342</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9156</v>
+        <v>-0.3459</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2441</v>
+        <v>0.1715</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.5314</v>
+        <v>-2.593</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7755</v>
+        <v>2.7645</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1392</v>
+        <v>0.6105</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.4237</v>
+        <v>-1.3457</v>
       </c>
       <c r="L4" t="n">
-        <v>3.563</v>
+        <v>1.9562</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1049</v>
+        <v>-0.439</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1077</v>
+        <v>-1.2474</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2126</v>
+        <v>0.8083</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6048</v>
+        <v>0.262</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0481</v>
+        <v>0.4273</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4433</v>
+        <v>-0.1653</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>1.7731</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1089</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8393</v>
+        <v>0.9737</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0342</v>
+        <v>0.1959</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8051</v>
+        <v>0.7779</v>
       </c>
       <c r="G5" t="n">
         <v>0.4201</v>
@@ -844,13 +844,13 @@
         <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2239</v>
+        <v>0.3583</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0138</v>
+        <v>0.1754</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2102</v>
+        <v>0.1829</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5461</v>
+        <v>0.305</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8189</v>
+        <v>0.4145</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2729</v>
+        <v>-0.1095</v>
       </c>
       <c r="G6" t="n">
         <v>2.886</v>
@@ -922,13 +922,13 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1875</v>
+        <v>0.9465</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8778</v>
+        <v>0.4733</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3097</v>
+        <v>0.4731</v>
       </c>
       <c r="V6" t="n">
         <v>-2.16</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5748</v>
+        <v>0.1802</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9277</v>
+        <v>-2.1999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3529</v>
+        <v>2.3801</v>
       </c>
       <c r="G7" t="n">
         <v>0.9644</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.1982</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8198</v>
+        <v>-0.092</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1334</v>
+        <v>-0.1061</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6946</v>
+        <v>-0.2218</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2153</v>
+        <v>-1.8514</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5207</v>
+        <v>1.6296</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0017</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3924</v>
+        <v>0.0805</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7592</v>
+        <v>-0.3954</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3669</v>
+        <v>0.4758</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9304</v>
+        <v>-0.8287</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3093</v>
+        <v>0.3292</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2397</v>
+        <v>-1.158</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3936</v>
@@ -1156,13 +1156,13 @@
         <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4865</v>
+        <v>0.5881</v>
       </c>
       <c r="T9" t="n">
-        <v>0.399</v>
+        <v>0.419</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1691</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2273</v>
+        <v>-1.085</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2722</v>
+        <v>-1.2117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.045</v>
+        <v>0.1267</v>
       </c>
       <c r="G10" t="n">
         <v>0.0114</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.0757</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1816</v>
+        <v>-0.121</v>
       </c>
       <c r="U10" t="n">
-        <v>0.115</v>
+        <v>0.1967</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9945</v>
+        <v>-2.9135</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.844</v>
+        <v>-1.8448</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1505</v>
+        <v>-1.0687</v>
       </c>
       <c r="G11" t="n">
         <v>0.5273</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0186</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1653</v>
+        <v>0.1646</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2648</v>
+        <v>-0.1831</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2735</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.627000000000001</v>
+        <v>-7.8171</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.303</v>
+        <v>-6.6564</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3241</v>
+        <v>-1.1607</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5989</v>
@@ -1390,13 +1390,13 @@
         <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3752</v>
+        <v>0.4347</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6382</v>
+        <v>0.0083</v>
       </c>
       <c r="U12" t="n">
-        <v>0.263</v>
+        <v>0.4264</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9414</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.822900000000002</v>
+        <v>-5.3099</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.1066</v>
+        <v>-9.593399999999999</v>
       </c>
       <c r="F13" t="n">
         <v>4.2836</v>
@@ -1468,13 +1468,13 @@
         <v>8.7904</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9078999999999999</v>
+        <v>2.4209</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6176999999999999</v>
+        <v>0.8953999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5257</v>
+        <v>1.5255</v>
       </c>
       <c r="V13" t="n">
         <v>-4.2651</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7193</v>
+        <v>5.8439</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7702</v>
+        <v>2.1635</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9491</v>
+        <v>3.6804</v>
       </c>
       <c r="G14" t="n">
         <v>3.026</v>
@@ -1546,13 +1546,13 @@
         <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4078</v>
+        <v>0.5324</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7651</v>
+        <v>0.1584</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3573</v>
+        <v>0.374</v>
       </c>
       <c r="V14" t="n">
         <v>0.3321</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8005</v>
+        <v>3.0322</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1896</v>
+        <v>2.886</v>
       </c>
       <c r="F15" t="n">
-        <v>2.611</v>
+        <v>0.1462</v>
       </c>
       <c r="G15" t="n">
-        <v>2.681</v>
+        <v>-0.6854</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9263</v>
+        <v>-0.1601</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7546</v>
+        <v>-0.5253</v>
       </c>
       <c r="J15" t="n">
-        <v>0.874</v>
+        <v>1.1575</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9273</v>
+        <v>0.738</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0533</v>
+        <v>0.4195</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8069</v>
+        <v>-1.8429</v>
       </c>
       <c r="N15" t="n">
-        <v>0.999</v>
+        <v>-0.8982</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8079</v>
+        <v>-0.9447</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0805</v>
+        <v>0.5772</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3787</v>
+        <v>-0.0446</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7019</v>
+        <v>0.6217</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.547</v>
+        <v>1.7731</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1097</v>
+        <v>1.7731</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3322</v>
+        <v>2.4255</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2336</v>
+        <v>1.0314</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0985</v>
+        <v>1.3941</v>
       </c>
       <c r="G16" t="n">
         <v>0.9612000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4529</v>
+        <v>0.5462</v>
       </c>
       <c r="T16" t="n">
-        <v>0.212</v>
+        <v>0.0098</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2408</v>
+        <v>0.5364</v>
       </c>
       <c r="V16" t="n">
         <v>0.3321</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6061</v>
+        <v>1.8735</v>
       </c>
       <c r="E17" t="n">
-        <v>1.976</v>
+        <v>-0.9227</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3699</v>
+        <v>2.7962</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6854</v>
+        <v>2.681</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1601</v>
+        <v>1.9263</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5253</v>
+        <v>0.7546</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1575</v>
+        <v>0.874</v>
       </c>
       <c r="K17" t="n">
-        <v>0.738</v>
+        <v>0.9273</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4195</v>
+        <v>-0.0533</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8429</v>
+        <v>1.8069</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8982</v>
+        <v>0.999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9447</v>
+        <v>0.8079</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.849</v>
+        <v>1.1535</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9546</v>
+        <v>0.2664</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1056</v>
+        <v>0.8871</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7731</v>
+        <v>-2.547</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7731</v>
+        <v>-0.1097</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0263</v>
+        <v>0.5241</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5217000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5481</v>
+        <v>0.4391</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3034</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1745</v>
+        <v>0.3233</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.1196</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5518</v>
+        <v>0.4429</v>
       </c>
       <c r="V18" t="n">
         <v>0.3321</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2526</v>
+        <v>0.4838</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8765</v>
+        <v>-1.5732</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6239</v>
+        <v>2.0569</v>
       </c>
       <c r="G19" t="n">
         <v>-0.547</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3465</v>
+        <v>-0.6101</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6808</v>
+        <v>-0.2477</v>
       </c>
       <c r="V19" t="n">
         <v>0.6642</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.319</v>
+        <v>-0.1842</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8352000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5162</v>
+        <v>0.651</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4538</v>
@@ -2014,13 +2014,13 @@
         <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4512</v>
+        <v>-0.3164</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2696</v>
+        <v>-0.1348</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5614</v>
+        <v>-0.9217</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1287</v>
+        <v>-2.8706</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5673</v>
+        <v>1.9489</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2027</v>
+        <v>-2.2215</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1842</v>
+        <v>1.9177</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3869</v>
+        <v>-4.1391</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7132</v>
+        <v>-1.9972</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2686</v>
+        <v>2.681</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9818</v>
+        <v>-4.6782</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4895</v>
+        <v>-0.2243</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0844</v>
+        <v>-0.7634</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4051</v>
+        <v>0.5391</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.618</v>
+        <v>0.2449</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3193</v>
+        <v>0.1033</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2986</v>
+        <v>0.1416</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3146</v>
+        <v>-1.0859</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0729</v>
+        <v>-0.0856</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7582</v>
+        <v>-1.0002</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2215</v>
+        <v>-1.2696</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9177</v>
+        <v>-1.0535</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.1391</v>
+        <v>-0.2161</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9972</v>
+        <v>1.1172</v>
       </c>
       <c r="K22" t="n">
-        <v>2.681</v>
+        <v>0.3888</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.6782</v>
+        <v>0.7284</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2243</v>
+        <v>-2.3868</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7634</v>
+        <v>-1.4423</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5391</v>
+        <v>-0.9445</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.148</v>
+        <v>-0.2888</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0989</v>
+        <v>-0.5034</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.049</v>
+        <v>0.2145</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5628</v>
+        <v>-1.126</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5278</v>
+        <v>-1.2245</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.035</v>
+        <v>0.0985</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3329</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6438</v>
+        <v>-0.207</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0219</v>
+        <v>0.1554</v>
       </c>
       <c r="V23" t="n">
         <v>1.2186</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.651</v>
+        <v>-1.3458</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4901</v>
+        <v>-2.9376</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1609</v>
+        <v>1.5918</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2696</v>
+        <v>-2.2027</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0535</v>
+        <v>0.1842</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2161</v>
+        <v>-2.3869</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1172</v>
+        <v>-1.7132</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3888</v>
+        <v>0.2686</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7284</v>
+        <v>-1.9818</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3868</v>
+        <v>-0.4895</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4423</v>
+        <v>-0.0844</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9445</v>
+        <v>-0.4051</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.854</v>
+        <v>-0.1664</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.4896</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0538</v>
+        <v>0.3232</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.823</v>
+        <v>9.519399999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2835</v>
+        <v>-4.2836</v>
       </c>
       <c r="F25" t="n">
-        <v>11.1065</v>
+        <v>13.8029</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3481</v>
+        <v>-4.348100000000001</v>
       </c>
       <c r="H25" t="n">
         <v>6.4404</v>
@@ -2377,13 +2377,13 @@
         <v>-10.7885</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4506000000000008</v>
+        <v>-0.4506000000000014</v>
       </c>
       <c r="K25" t="n">
-        <v>8.307500000000001</v>
+        <v>8.307499999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-8.758199999999999</v>
+        <v>-8.7582</v>
       </c>
       <c r="M25" t="n">
         <v>-3.8976</v>
@@ -2395,7 +2395,7 @@
         <v>-2.0303</v>
       </c>
       <c r="P25" t="n">
-        <v>7.813599999999998</v>
+        <v>7.813599999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-8.7903</v>
@@ -2404,19 +2404,19 @@
         <v>16.6042</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9078000000000003</v>
+        <v>1.7888</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.5255</v>
+        <v>-1.5257</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6176999999999999</v>
+        <v>3.3143</v>
       </c>
       <c r="V25" t="n">
         <v>4.2652</v>
       </c>
       <c r="W25" t="n">
-        <v>6.4829</v>
+        <v>6.482900000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-2.2178</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484222_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484222_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.1089</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.305</v>
+        <v>0.914</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4145</v>
+        <v>0.914</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1095</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.886</v>
+        <v>0.914</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9849</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9011</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2267</v>
+        <v>0.914</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5387</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6879</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6593</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5538</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2132</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9465</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4733</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4731</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SANTOLARIA MORENO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1802</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1999</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3801</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9644</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4515</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4159</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1545</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4515</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.606</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.903</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.0219</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.092</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1061</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2218</v>
+        <v>0.305</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8514</v>
+        <v>0.4145</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6296</v>
+        <v>-0.1095</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0017</v>
+        <v>2.886</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8667</v>
+        <v>0.9849</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.135</v>
+        <v>1.9011</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.456</v>
+        <v>2.2267</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.243</v>
+        <v>1.5387</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.213</v>
+        <v>0.6879</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4543</v>
+        <v>0.6593</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6237</v>
+        <v>-0.5538</v>
       </c>
       <c r="O8" t="n">
-        <v>1.078</v>
+        <v>1.2132</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0805</v>
+        <v>0.9465</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3954</v>
+        <v>0.4733</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4758</v>
+        <v>0.4731</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>-2.16</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>D. SANTOLARIA MORENO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8287</v>
+        <v>0.1802</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3292</v>
+        <v>-2.1999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.158</v>
+        <v>2.3801</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3936</v>
+        <v>0.9644</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9463</v>
+        <v>-0.4515</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5527</v>
+        <v>1.4159</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7698</v>
+        <v>-0.1545</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0819</v>
+        <v>0.4515</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6879</v>
+        <v>-0.606</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1634</v>
+        <v>1.1189</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0281</v>
+        <v>-0.903</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1352</v>
+        <v>2.0219</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5881</v>
+        <v>-0.1982</v>
       </c>
       <c r="T9" t="n">
-        <v>0.419</v>
+        <v>-0.092</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1691</v>
+        <v>-0.1061</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.085</v>
+        <v>-0.8287</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2117</v>
+        <v>0.3292</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1267</v>
+        <v>-1.158</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0114</v>
+        <v>-0.3936</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0289</v>
+        <v>-0.9463</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0403</v>
+        <v>0.5527</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0814</v>
+        <v>0.7698</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0409</v>
+        <v>0.0819</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>0.6879</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.1634</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0698</v>
+        <v>-1.0281</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0002</v>
+        <v>-0.1352</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0757</v>
+        <v>0.5881</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.121</v>
+        <v>0.419</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1967</v>
+        <v>0.1691</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9135</v>
+        <v>-1.085</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8448</v>
+        <v>-1.2117</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0687</v>
+        <v>0.1267</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5273</v>
+        <v>0.0114</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0123</v>
+        <v>-0.0289</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.485</v>
+        <v>0.0403</v>
       </c>
       <c r="J11" t="n">
-        <v>1.171</v>
+        <v>0.0814</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5991</v>
+        <v>0.0409</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4281</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6437</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5868</v>
+        <v>-0.0698</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9431</v>
+        <v>-0.0002</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0186</v>
+        <v>0.0757</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1646</v>
+        <v>-0.121</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1831</v>
+        <v>0.1967</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2735</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8171</v>
+        <v>-1.1358</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.6564</v>
+        <v>-2.7654</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1607</v>
+        <v>1.6296</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5989</v>
+        <v>-1.9157</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6974</v>
+        <v>-1.1737</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9015</v>
+        <v>-0.742</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.8398</v>
+        <v>-2.37</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9389</v>
+        <v>-0.55</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9009</v>
+        <v>-1.82</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7591</v>
+        <v>0.4543</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7585</v>
+        <v>-0.6237</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>1.078</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.7115</v>
+        <v>0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4347</v>
+        <v>0.0805</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0083</v>
+        <v>-0.3954</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4264</v>
+        <v>0.4758</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,229 +1483,240 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3099</v>
+        <v>-2.9135</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.593399999999999</v>
+        <v>-1.8448</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2836</v>
+        <v>-1.0687</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3483</v>
+        <v>0.5273</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.440300000000001</v>
+        <v>1.0123</v>
       </c>
       <c r="I13" t="n">
-        <v>10.7886</v>
+        <v>-0.485</v>
       </c>
       <c r="J13" t="n">
-        <v>3.897500000000001</v>
+        <v>1.171</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8673</v>
+        <v>2.5991</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0303</v>
+        <v>-1.4281</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4507</v>
+        <v>-0.6437</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.307600000000001</v>
+        <v>-1.5868</v>
       </c>
       <c r="O13" t="n">
-        <v>8.7584</v>
+        <v>0.9431</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.8138</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.6041</v>
+        <v>-3.1255</v>
       </c>
       <c r="R13" t="n">
-        <v>8.7904</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4209</v>
+        <v>-0.0186</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8953999999999999</v>
+        <v>0.1646</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5255</v>
+        <v>-0.1831</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.2651</v>
+        <v>-1.2735</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2177</v>
+        <v>-0.0549</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.482900000000001</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8439</v>
+        <v>-8.1241</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1635</v>
+        <v>-6.9634</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6804</v>
+        <v>-1.1607</v>
       </c>
       <c r="G14" t="n">
-        <v>3.026</v>
+        <v>-3.9059</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3643</v>
+        <v>-2.0044</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6617</v>
+        <v>-1.9015</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1539</v>
+        <v>-3.1468</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4351</v>
+        <v>-1.2459</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2813</v>
+        <v>-1.9009</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8721</v>
+        <v>-0.7591</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9292</v>
+        <v>-0.7585</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9429</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9534</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9301</v>
+        <v>0.3907</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5324</v>
+        <v>0.4347</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1584</v>
+        <v>0.0083</v>
       </c>
       <c r="U14" t="n">
-        <v>0.374</v>
+        <v>0.4264</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3321</v>
+        <v>-0.9414</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>FRIVALCA LA MUELA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0322</v>
+        <v>-5.309899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.886</v>
+        <v>-9.593399999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1462</v>
+        <v>4.2836</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6854</v>
+        <v>4.348300000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1601</v>
+        <v>-6.440300000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5253</v>
+        <v>10.7886</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1575</v>
+        <v>3.897500000000002</v>
       </c>
       <c r="K15" t="n">
-        <v>0.738</v>
+        <v>1.8673</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4195</v>
+        <v>2.0303</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8429</v>
+        <v>0.4507</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8982</v>
+        <v>-8.307600000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9447</v>
+        <v>8.7584</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-7.8138</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-16.6041</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>8.7904</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5772</v>
+        <v>2.4209</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0446</v>
+        <v>0.8953999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6217</v>
+        <v>1.5255</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7731</v>
+        <v>-4.2651</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>2.2177</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-6.482900000000001</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4255</v>
+        <v>5.8439</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0314</v>
+        <v>2.1635</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3941</v>
+        <v>3.6804</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9612000000000001</v>
+        <v>3.026</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0141</v>
+        <v>2.3643</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0529</v>
+        <v>0.6617</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7211</v>
+        <v>1.1539</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5592</v>
+        <v>1.4351</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1619</v>
+        <v>-0.2813</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7599</v>
+        <v>1.8721</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4549</v>
+        <v>0.9292</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2148</v>
+        <v>0.9429</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5462</v>
+        <v>0.5324</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0098</v>
+        <v>0.1584</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5364</v>
+        <v>0.374</v>
       </c>
       <c r="V16" t="n">
         <v>0.3321</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>1.8279</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0549</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8735</v>
+        <v>3.0322</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9227</v>
+        <v>2.886</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7962</v>
+        <v>0.1462</v>
       </c>
       <c r="G17" t="n">
-        <v>2.681</v>
+        <v>-0.6854</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9263</v>
+        <v>-0.1601</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7546</v>
+        <v>-0.5253</v>
       </c>
       <c r="J17" t="n">
-        <v>0.874</v>
+        <v>1.1575</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9273</v>
+        <v>0.738</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0533</v>
+        <v>0.4195</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8069</v>
+        <v>-1.8429</v>
       </c>
       <c r="N17" t="n">
-        <v>0.999</v>
+        <v>-0.8982</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8079</v>
+        <v>-0.9447</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1535</v>
+        <v>0.5772</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2664</v>
+        <v>-0.0446</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8871</v>
+        <v>0.6217</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.547</v>
+        <v>1.7731</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1097</v>
+        <v>1.7731</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5241</v>
+        <v>2.4255</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0849</v>
+        <v>1.0314</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4391</v>
+        <v>1.3941</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3034</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1545</v>
+        <v>2.0141</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1488</v>
+        <v>-1.0529</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2045</v>
+        <v>1.7211</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08309999999999999</v>
+        <v>1.5592</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1214</v>
+        <v>0.1619</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5079</v>
+        <v>-0.7599</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2377</v>
+        <v>0.4549</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2702</v>
+        <v>-1.2148</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3233</v>
+        <v>0.5462</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1196</v>
+        <v>0.0098</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4429</v>
+        <v>0.5364</v>
       </c>
       <c r="V18" t="n">
         <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4838</v>
+        <v>1.8735</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5732</v>
+        <v>-0.9227</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0569</v>
+        <v>2.7962</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.547</v>
+        <v>2.681</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7475000000000001</v>
+        <v>1.9263</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2945</v>
+        <v>0.7546</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2108</v>
+        <v>0.874</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.9273</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2939</v>
+        <v>-0.0533</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6637999999999999</v>
+        <v>1.8069</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6644</v>
+        <v>0.999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.8079</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6101</v>
+        <v>1.1535</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3624</v>
+        <v>0.2664</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2477</v>
+        <v>0.8871</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6642</v>
+        <v>-2.547</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.1097</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1842</v>
+        <v>0.5241</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8352000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="F20" t="n">
-        <v>0.651</v>
+        <v>0.4391</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4538</v>
+        <v>-1.3034</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0494</v>
+        <v>-1.1545</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4045</v>
+        <v>-0.1488</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6536</v>
+        <v>0.2045</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0205</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>0.1214</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1998</v>
+        <v>-1.5079</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0698</v>
+        <v>-1.2377</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2696</v>
+        <v>-0.2702</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3164</v>
+        <v>0.3233</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1816</v>
+        <v>-0.1196</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1348</v>
+        <v>0.4429</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2143,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9217</v>
+        <v>0.4838</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8706</v>
+        <v>-1.5732</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9489</v>
+        <v>2.0569</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2215</v>
+        <v>-0.547</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9177</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.1391</v>
+        <v>-1.2945</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9972</v>
+        <v>-1.2108</v>
       </c>
       <c r="K21" t="n">
-        <v>2.681</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.6782</v>
+        <v>-1.2939</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2243</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7634</v>
+        <v>0.6644</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5391</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2449</v>
+        <v>-0.6101</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1033</v>
+        <v>-0.3624</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1416</v>
+        <v>-0.2477</v>
       </c>
       <c r="V21" t="n">
         <v>0.6642</v>
@@ -2108,12 +2204,17 @@
       </c>
       <c r="X21" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0859</v>
+        <v>-0.1842</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0856</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0002</v>
+        <v>0.651</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2696</v>
+        <v>-0.4538</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0535</v>
+        <v>-0.0494</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2161</v>
+        <v>-0.4045</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1172</v>
+        <v>-0.6536</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3888</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7284</v>
+        <v>-0.6741</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3868</v>
+        <v>0.1998</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4423</v>
+        <v>-0.0698</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9445</v>
+        <v>0.2696</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2888</v>
+        <v>-0.3164</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5034</v>
+        <v>-0.1816</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2145</v>
+        <v>-0.1348</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.126</v>
+        <v>-0.9217</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2245</v>
+        <v>-2.8706</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0985</v>
+        <v>1.9489</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3329</v>
+        <v>-2.2215</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2962</v>
+        <v>1.9177</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0367</v>
+        <v>-4.1391</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.104</v>
+        <v>-1.9972</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1228</v>
+        <v>2.681</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2268</v>
+        <v>-4.6782</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2289</v>
+        <v>-0.2243</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.419</v>
+        <v>-0.7634</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8099</v>
+        <v>0.5391</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.207</v>
+        <v>0.2449</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3624</v>
+        <v>0.1033</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1554</v>
+        <v>0.1416</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3458</v>
+        <v>-1.0859</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9376</v>
+        <v>-0.0856</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5918</v>
+        <v>-1.0002</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2027</v>
+        <v>-1.2696</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1842</v>
+        <v>-1.0535</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3869</v>
+        <v>-0.2161</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7132</v>
+        <v>1.1172</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2686</v>
+        <v>0.3888</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9818</v>
+        <v>0.7284</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4895</v>
+        <v>-2.3868</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0844</v>
+        <v>-1.4423</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4051</v>
+        <v>-0.9445</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1664</v>
+        <v>-0.2888</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4896</v>
+        <v>-0.5034</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3232</v>
+        <v>0.2145</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.126</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.2245</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.3329</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2962</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.0367</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.104</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.2268</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.2289</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.419</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.8099</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.207</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3624</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. CANO CANO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.3458</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.9376</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.5918</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.2027</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.3869</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.7132</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.9818</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.4895</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.1664</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.4896</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484222_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>9.519399999999997</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>-4.2836</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>13.8029</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G27" t="n">
         <v>-4.348100000000001</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H27" t="n">
         <v>6.4404</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I27" t="n">
         <v>-10.7885</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J27" t="n">
         <v>-0.4506000000000014</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K27" t="n">
         <v>8.307499999999999</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L27" t="n">
         <v>-8.7582</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M27" t="n">
         <v>-3.8976</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-1.8673</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>-2.0303</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>7.813599999999999</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-8.7903</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>16.6042</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S27" t="n">
         <v>1.7888</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>-1.5257</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>3.3143</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>4.2652</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>6.482900000000001</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-2.2178</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
